--- a/Data/Qualitative analysis results/Pure human.xlsx
+++ b/Data/Qualitative analysis results/Pure human.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xingqian/Desktop/msr_replication_package/Data/Qualitative analysis results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xingqian/Desktop/PR_replication_package/Data/Qualitative analysis results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A4773F-12A0-4241-8E4A-110C3F006E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EEAA47F-3526-814B-90BB-1A8C2BECFE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3260" yWindow="2260" windowWidth="28040" windowHeight="17180" xr2:uid="{B1AB028F-657B-ED48-ACEC-D0413BECC894}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="215">
   <si>
     <t>Pure Human</t>
   </si>
@@ -489,13 +489,205 @@
   </si>
   <si>
     <t>https://github.com/goat-sdk/goat/pull/429/commits/f381a8e3f02c91453a41c25d834cc0b95bd7aaf4</t>
+  </si>
+  <si>
+    <t>https://github.com/AMaestroG/condadodecastilla.com/pull/6</t>
+  </si>
+  <si>
+    <t>https://github.com/AMaestroG/condadodecastilla.com/pull/314</t>
+  </si>
+  <si>
+    <t>https://github.com/Agoric/documentation/pull/841</t>
+  </si>
+  <si>
+    <t>https://github.com/Agoric/documentation/pull/1226</t>
+  </si>
+  <si>
+    <t>https://github.com/Argus-Labs/world-cli/pull/162</t>
+  </si>
+  <si>
+    <t>https://github.com/Argus-Labs/world-cli/pull/166</t>
+  </si>
+  <si>
+    <t>https://github.com/Argus-Labs/world-cli/pull/175</t>
+  </si>
+  <si>
+    <t>https://github.com/Argus-Labs/world-cli/pull/187</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/LogicAppsUX/pull/4958</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/LogicAppsUX/pull/6440</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/LogicAppsUX/pull/7649</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/LogicAppsUX/pull/7834</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/LogicAppsUX/pull/8458</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/LogicAppsUX/pull/8801</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-go/pull/14549</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-go/pull/21177</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-go/pull/21461</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-go/pull/21804</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/4515</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/4529</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/5601</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/5732</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/6028</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/16836</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/24351</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/24762</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/27524</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/31062</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/31614</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/33675</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/33714</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/35192</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/35955</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/36010</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/38370</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/45398</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/48861</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/55570</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/56537</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-net/pull/56791</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-python/pull/136</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-python/pull/6442</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-python/pull/7848</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-python/pull/24878</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-python/pull/24931</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-python/pull/32743</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-python/pull/32788</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-python/pull/36664</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-python/pull/39578</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-python/pull/41882</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-python/pull/43196</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-for-python/pull/44364</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-tools/pull/1797</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-sdk-tools/pull/3987</t>
+  </si>
+  <si>
+    <t>direct removal</t>
+  </si>
+  <si>
+    <t>move method</t>
+  </si>
+  <si>
+    <t>Parameterize Method</t>
+  </si>
+  <si>
+    <t>extract class</t>
+  </si>
+  <si>
+    <t>extract superclass</t>
+  </si>
+  <si>
+    <t>Consolidate Constructors</t>
+  </si>
+  <si>
+    <t>Move class</t>
+  </si>
+  <si>
+    <t>pull up method</t>
+  </si>
+  <si>
+    <t>replace value with constants</t>
+  </si>
+  <si>
+    <t>Direct removal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -526,6 +718,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -548,7 +747,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -557,11 +756,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -897,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B926ADE2-A84F-1540-804C-136F826C5CFF}">
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P102"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="12" max="12" width="32.83203125" customWidth="1"/>
@@ -909,20 +1109,20 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4" t="s">
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4" t="s">
+      <c r="G1" s="6"/>
+      <c r="H1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="4"/>
+      <c r="I1" s="6"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
@@ -1017,10 +1217,10 @@
       <c r="K3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="5" t="s">
         <v>68</v>
       </c>
       <c r="N3" s="1" t="s">
@@ -1061,10 +1261,10 @@
       <c r="K4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="5" t="s">
         <v>70</v>
       </c>
       <c r="N4" s="1" t="s">
@@ -1105,10 +1305,10 @@
       <c r="K5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="5" t="s">
         <v>72</v>
       </c>
       <c r="N5" s="1" t="s">
@@ -1149,10 +1349,10 @@
       <c r="K6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="M6" s="5" t="s">
         <v>74</v>
       </c>
       <c r="N6" s="1" t="s">
@@ -1193,10 +1393,10 @@
       <c r="K7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="M7" s="5" t="s">
         <v>76</v>
       </c>
       <c r="N7" s="1" t="s">
@@ -1240,10 +1440,10 @@
       <c r="K8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="M8" s="5" t="s">
         <v>78</v>
       </c>
       <c r="N8" s="1" t="s">
@@ -1284,10 +1484,10 @@
       <c r="K9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="M9" s="5" t="s">
         <v>80</v>
       </c>
       <c r="N9" s="1" t="s">
@@ -1328,10 +1528,10 @@
       <c r="K10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="5" t="s">
         <v>82</v>
       </c>
       <c r="N10" s="1" t="s">
@@ -1372,10 +1572,10 @@
       <c r="K11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="M11" s="5" t="s">
         <v>84</v>
       </c>
       <c r="N11" s="1" t="s">
@@ -1416,10 +1616,10 @@
       <c r="K12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L12" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="M12" s="6" t="s">
+      <c r="M12" s="5" t="s">
         <v>86</v>
       </c>
       <c r="N12" s="1" t="s">
@@ -1463,10 +1663,10 @@
       <c r="K13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L13" s="6" t="s">
+      <c r="L13" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="M13" s="6" t="s">
+      <c r="M13" s="5" t="s">
         <v>88</v>
       </c>
       <c r="N13" s="1" t="s">
@@ -1507,10 +1707,10 @@
       <c r="K14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L14" s="6" t="s">
+      <c r="L14" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="M14" s="6" t="s">
+      <c r="M14" s="5" t="s">
         <v>90</v>
       </c>
       <c r="N14" s="1" t="s">
@@ -1551,10 +1751,10 @@
       <c r="K15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="L15" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="M15" s="5" t="s">
         <v>92</v>
       </c>
       <c r="N15" s="1" t="s">
@@ -1595,10 +1795,10 @@
       <c r="K16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L16" s="6" t="s">
+      <c r="L16" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="M16" s="6" t="s">
+      <c r="M16" s="5" t="s">
         <v>94</v>
       </c>
       <c r="N16" s="1" t="s">
@@ -1639,10 +1839,10 @@
       <c r="K17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L17" s="6" t="s">
+      <c r="L17" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="M17" s="6" t="s">
+      <c r="M17" s="5" t="s">
         <v>96</v>
       </c>
       <c r="N17" s="1" t="s">
@@ -1683,10 +1883,10 @@
       <c r="K18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="L18" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="M18" s="6" t="s">
+      <c r="M18" s="5" t="s">
         <v>98</v>
       </c>
       <c r="N18" s="1" t="s">
@@ -1730,10 +1930,10 @@
       <c r="K19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L19" s="6" t="s">
+      <c r="L19" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="M19" s="5"/>
+      <c r="M19" s="4"/>
       <c r="N19" s="1" t="s">
         <v>44</v>
       </c>
@@ -1772,10 +1972,10 @@
       <c r="K20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L20" s="6" t="s">
+      <c r="L20" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="M20" s="6" t="s">
+      <c r="M20" s="5" t="s">
         <v>101</v>
       </c>
       <c r="N20" s="1" t="s">
@@ -1816,10 +2016,10 @@
       <c r="K21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L21" s="6" t="s">
+      <c r="L21" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="M21" s="5"/>
+      <c r="M21" s="4"/>
       <c r="N21" s="1" t="s">
         <v>45</v>
       </c>
@@ -1862,10 +2062,10 @@
       <c r="K22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L22" s="6" t="s">
+      <c r="L22" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="M22" s="6" t="s">
+      <c r="M22" s="5" t="s">
         <v>104</v>
       </c>
       <c r="N22" s="1" t="s">
@@ -1909,10 +2109,10 @@
       <c r="K23" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L23" s="6" t="s">
+      <c r="L23" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="M23" s="6" t="s">
+      <c r="M23" s="5" t="s">
         <v>106</v>
       </c>
       <c r="N23" s="1" t="s">
@@ -1953,10 +2153,10 @@
       <c r="K24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L24" s="6" t="s">
+      <c r="L24" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="M24" s="6" t="s">
+      <c r="M24" s="5" t="s">
         <v>108</v>
       </c>
       <c r="N24" s="1" t="s">
@@ -1997,10 +2197,10 @@
       <c r="K25" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L25" s="6" t="s">
+      <c r="L25" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="M25" s="6" t="s">
+      <c r="M25" s="5" t="s">
         <v>110</v>
       </c>
       <c r="N25" s="1" t="s">
@@ -2041,10 +2241,10 @@
       <c r="K26" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L26" s="6" t="s">
+      <c r="L26" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="M26" s="6" t="s">
+      <c r="M26" s="5" t="s">
         <v>112</v>
       </c>
       <c r="N26" s="1" t="s">
@@ -2085,10 +2285,10 @@
       <c r="K27" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L27" s="6" t="s">
+      <c r="L27" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="M27" s="6" t="s">
+      <c r="M27" s="5" t="s">
         <v>114</v>
       </c>
       <c r="N27" s="1" t="s">
@@ -2129,10 +2329,10 @@
       <c r="K28" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L28" s="6" t="s">
+      <c r="L28" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="M28" s="6" t="s">
+      <c r="M28" s="5" t="s">
         <v>116</v>
       </c>
       <c r="N28" s="1" t="s">
@@ -2173,10 +2373,10 @@
       <c r="K29" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L29" s="6" t="s">
+      <c r="L29" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="M29" s="6" t="s">
+      <c r="M29" s="5" t="s">
         <v>118</v>
       </c>
       <c r="N29" s="1" t="s">
@@ -2221,10 +2421,10 @@
       <c r="K30" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L30" s="6" t="s">
+      <c r="L30" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="M30" s="5"/>
+      <c r="M30" s="4"/>
       <c r="N30" s="1" t="s">
         <v>48</v>
       </c>
@@ -2263,10 +2463,10 @@
       <c r="K31" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L31" s="6" t="s">
+      <c r="L31" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="M31" s="6" t="s">
+      <c r="M31" s="5" t="s">
         <v>121</v>
       </c>
       <c r="N31" s="1" t="s">
@@ -2307,10 +2507,10 @@
       <c r="K32" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L32" s="6" t="s">
+      <c r="L32" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="M32" s="6" t="s">
+      <c r="M32" s="5" t="s">
         <v>123</v>
       </c>
       <c r="N32" s="1" t="s">
@@ -2354,10 +2554,10 @@
       <c r="K33" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L33" s="6" t="s">
+      <c r="L33" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="M33" s="6" t="s">
+      <c r="M33" s="5" t="s">
         <v>125</v>
       </c>
       <c r="N33" s="1" t="s">
@@ -2398,10 +2598,10 @@
       <c r="K34" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L34" s="6" t="s">
+      <c r="L34" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="M34" s="6" t="s">
+      <c r="M34" s="5" t="s">
         <v>127</v>
       </c>
       <c r="N34" s="1" t="s">
@@ -2442,10 +2642,10 @@
       <c r="K35" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L35" s="6" t="s">
+      <c r="L35" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="M35" s="6" t="s">
+      <c r="M35" s="5" t="s">
         <v>129</v>
       </c>
       <c r="N35" s="1" t="s">
@@ -2486,10 +2686,10 @@
       <c r="K36" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L36" s="6" t="s">
+      <c r="L36" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="M36" s="6" t="s">
+      <c r="M36" s="5" t="s">
         <v>131</v>
       </c>
       <c r="N36" s="1" t="s">
@@ -2533,10 +2733,10 @@
       <c r="K37" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L37" s="6" t="s">
+      <c r="L37" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="M37" s="6" t="s">
+      <c r="M37" s="5" t="s">
         <v>133</v>
       </c>
       <c r="N37" s="1" t="s">
@@ -2577,10 +2777,10 @@
       <c r="K38" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L38" s="6" t="s">
+      <c r="L38" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="M38" s="6" t="s">
+      <c r="M38" s="5" t="s">
         <v>135</v>
       </c>
       <c r="N38" s="1" t="s">
@@ -2621,10 +2821,10 @@
       <c r="K39" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L39" s="6" t="s">
+      <c r="L39" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="M39" s="5"/>
+      <c r="M39" s="4"/>
       <c r="N39" s="1" t="s">
         <v>49</v>
       </c>
@@ -2663,10 +2863,10 @@
       <c r="K40" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L40" s="6" t="s">
+      <c r="L40" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M40" s="5"/>
+      <c r="M40" s="4"/>
       <c r="N40" s="1" t="s">
         <v>49</v>
       </c>
@@ -2709,10 +2909,10 @@
       <c r="K41" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L41" s="6" t="s">
+      <c r="L41" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="M41" s="6" t="s">
+      <c r="M41" s="5" t="s">
         <v>139</v>
       </c>
       <c r="N41" s="1" t="s">
@@ -2753,10 +2953,10 @@
       <c r="K42" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L42" s="6" t="s">
+      <c r="L42" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="M42" s="6" t="s">
+      <c r="M42" s="5" t="s">
         <v>141</v>
       </c>
       <c r="N42" s="1" t="s">
@@ -2800,10 +3000,10 @@
       <c r="K43" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L43" s="6" t="s">
+      <c r="L43" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="M43" s="6" t="s">
+      <c r="M43" s="5" t="s">
         <v>143</v>
       </c>
       <c r="N43" s="1" t="s">
@@ -2844,10 +3044,10 @@
       <c r="K44" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L44" s="6" t="s">
+      <c r="L44" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="M44" s="6" t="s">
+      <c r="M44" s="5" t="s">
         <v>145</v>
       </c>
       <c r="N44" s="1" t="s">
@@ -2891,10 +3091,10 @@
       <c r="K45" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L45" s="6" t="s">
+      <c r="L45" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="M45" s="5"/>
+      <c r="M45" s="4"/>
       <c r="N45" s="1" t="s">
         <v>48</v>
       </c>
@@ -2933,10 +3133,10 @@
       <c r="K46" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L46" s="6" t="s">
+      <c r="L46" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="M46" s="6" t="s">
+      <c r="M46" s="5" t="s">
         <v>148</v>
       </c>
       <c r="N46" s="1" t="s">
@@ -2980,10 +3180,10 @@
       <c r="K47" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L47" s="6" t="s">
+      <c r="L47" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="M47" s="6" t="s">
+      <c r="M47" s="5" t="s">
         <v>150</v>
       </c>
       <c r="N47" s="1" t="s">
@@ -2994,6 +3194,2261 @@
       </c>
       <c r="P47" s="1" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A48" s="7">
+        <v>2551754588</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L48" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A49" s="7">
+        <v>2580869291</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L49" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A50" s="7">
+        <v>1472173649</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L50" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A51" s="7">
+        <v>2103851517</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L51" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A52" s="7">
+        <v>2504766847</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L52" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A53" s="7">
+        <v>2505216777</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L53" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A54" s="7">
+        <v>2524719291</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L54" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A55" s="7">
+        <v>2537678634</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L55" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A56" s="7">
+        <v>1913141543</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L56" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A57" s="7">
+        <v>2290754176</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L57" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A58" s="7">
+        <v>2619449191</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L58" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A59" s="7">
+        <v>2674860759</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L59" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A60" s="7">
+        <v>2948740463</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L60" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A61" s="7">
+        <v>3264459764</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L61" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A62" s="7">
+        <v>2551754588</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L62" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A63" s="7">
+        <v>617778038</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L63" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="N63" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A64" s="7">
+        <v>1435217554</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L64" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="N64" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A65" s="7">
+        <v>1494678824</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L65" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="N65" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A66" s="7">
+        <v>1563670931</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L66" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A67" s="7">
+        <v>198456270</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L67" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A68" s="7">
+        <v>199807313</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L68" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A69" s="7">
+        <v>264721561</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L69" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A70" s="7">
+        <v>268439787</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L70" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="N70" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A71" s="7">
+        <v>275127076</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L71" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A72" s="7">
+        <v>518725714</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L72" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="N72" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A73" s="7">
+        <v>747125142</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L73" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="N73" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A74" s="7">
+        <v>759564609</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L74" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="N74" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A75" s="7">
+        <v>878003498</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L75" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="N75" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A76" s="7">
+        <v>1053670623</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L76" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="N76" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A77" s="7">
+        <v>1077882644</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L77" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="N77" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A78" s="7">
+        <v>1216983899</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L78" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="N78" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A79" s="7">
+        <v>1219873147</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L79" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="N79" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A80" s="7">
+        <v>1293405006</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L80" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="N80" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A81" s="7">
+        <v>1336925159</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L81" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="N81" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A82" s="7">
+        <v>1339018801</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L82" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="N82" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A83" s="7">
+        <v>1490252198</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L83" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="N83" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A84" s="7">
+        <v>2009382290</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L84" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="N84" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A85" s="7">
+        <v>2394209636</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L85" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="N85" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A86" s="7">
+        <v>3256601866</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L86" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="N86" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A87" s="7">
+        <v>3333496020</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L87" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="N87" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A88" s="7">
+        <v>3356188435</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L88" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="N88" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A89" s="7">
+        <v>13172257</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L89" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="N89" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A90" s="7">
+        <v>300032891</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L90" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="N90" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A91" s="7">
+        <v>327411057</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L91" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="N91" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A92" s="7">
+        <v>968782764</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L92" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="N92" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A93" s="7">
+        <v>974074937</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L93" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="N93" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A94" s="7">
+        <v>1573620027</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L94" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="N94" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A95" s="7">
+        <v>1575819010</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L95" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="N95" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A96" s="7">
+        <v>1991334185</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L96" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="N96" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A97" s="7">
+        <v>2317688255</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L97" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="N97" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A98" s="7">
+        <v>2636722184</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L98" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="N98" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A99" s="7">
+        <v>2875364035</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L99" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="N99" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A100" s="7">
+        <v>3088848545</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L100" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="N100" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A101" s="7">
+        <v>687045037</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L101" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="N101" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A102" s="7">
+        <v>1031584503</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L102" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="N102" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -3087,6 +5542,61 @@
     <hyperlink ref="M46" r:id="rId82" xr:uid="{881E5BED-D4A2-B842-9D28-0B323C094BBE}"/>
     <hyperlink ref="L47" r:id="rId83" xr:uid="{D662D3E4-BEC7-4845-826D-06F84A9F3393}"/>
     <hyperlink ref="M47" r:id="rId84" xr:uid="{5E843A82-BE08-ED47-8D14-2BD1FA6E4BAD}"/>
+    <hyperlink ref="L48" r:id="rId85" xr:uid="{7EEB9685-964F-C744-84B8-4CB6330DF581}"/>
+    <hyperlink ref="L49" r:id="rId86" xr:uid="{5FD1D22A-C18D-E74E-9330-E11A81FCFEA1}"/>
+    <hyperlink ref="L50" r:id="rId87" xr:uid="{19B362D9-D553-0F4B-8A07-D0659AB39DFB}"/>
+    <hyperlink ref="L51" r:id="rId88" xr:uid="{F7BF0851-D65D-6448-9066-CB7D0B455374}"/>
+    <hyperlink ref="L52" r:id="rId89" xr:uid="{5E13C3A3-9AFF-B84D-8DB7-39DA62FF023F}"/>
+    <hyperlink ref="L53" r:id="rId90" xr:uid="{ED6378EB-EFC2-B74A-8128-3131B3DCE1DF}"/>
+    <hyperlink ref="L54" r:id="rId91" xr:uid="{9BBE6356-0632-3043-8568-BFB550CC71D9}"/>
+    <hyperlink ref="L55" r:id="rId92" xr:uid="{AA0AFB7B-40C5-1248-A309-3EE549AED777}"/>
+    <hyperlink ref="L56" r:id="rId93" xr:uid="{EA29FFC6-3DE6-0C41-8B4D-BC9BEB269FFD}"/>
+    <hyperlink ref="L57" r:id="rId94" xr:uid="{CF506259-0A06-834C-AAF0-DCDB3377805D}"/>
+    <hyperlink ref="L58" r:id="rId95" xr:uid="{A69E4287-AAEC-494E-8304-F5788E15E0E5}"/>
+    <hyperlink ref="L59" r:id="rId96" xr:uid="{2B03641A-2153-2745-A899-AA206D1D5526}"/>
+    <hyperlink ref="L60" r:id="rId97" xr:uid="{9A1D5629-A58A-4543-A7F4-9B606B144CA4}"/>
+    <hyperlink ref="L61" r:id="rId98" xr:uid="{7F5CCAB2-40BE-A244-85EF-1FCBE06BC584}"/>
+    <hyperlink ref="L63" r:id="rId99" xr:uid="{916A5A07-6953-5246-ABFF-24327AAA558D}"/>
+    <hyperlink ref="L64" r:id="rId100" xr:uid="{5305138E-216D-9B4F-8AA6-0816D11CC314}"/>
+    <hyperlink ref="L65" r:id="rId101" xr:uid="{887BC19D-892B-0048-8297-A4D6A1C48872}"/>
+    <hyperlink ref="L66" r:id="rId102" xr:uid="{B1E23242-E061-5E4B-A4B8-B891604385B8}"/>
+    <hyperlink ref="L67" r:id="rId103" xr:uid="{5E40B340-AE2D-B049-948D-8D5C5A3398EF}"/>
+    <hyperlink ref="L68" r:id="rId104" xr:uid="{F4188B31-A5DC-2D43-89A4-669D12358AD7}"/>
+    <hyperlink ref="L69" r:id="rId105" xr:uid="{AF330137-2EDC-A141-8AFE-81EACF5B1C77}"/>
+    <hyperlink ref="L70" r:id="rId106" xr:uid="{21146D30-E10C-EF49-AF8C-0E9A3859575A}"/>
+    <hyperlink ref="L71" r:id="rId107" xr:uid="{A3EBDF55-5F31-8940-A77A-E16DE33DAF84}"/>
+    <hyperlink ref="L72" r:id="rId108" xr:uid="{48739EE9-1969-4C4F-BB05-6723234E35E2}"/>
+    <hyperlink ref="L73" r:id="rId109" xr:uid="{4D9549C2-6E9F-7645-AA6F-B3A5817AB97B}"/>
+    <hyperlink ref="L74" r:id="rId110" xr:uid="{DDC8E94E-CADA-4049-AE52-C55F110D7079}"/>
+    <hyperlink ref="L75" r:id="rId111" xr:uid="{98ABCFA6-25E0-B440-9806-7342BE597C89}"/>
+    <hyperlink ref="L76" r:id="rId112" xr:uid="{AAFCF679-C5C5-D544-BDA7-2AE5E223B92B}"/>
+    <hyperlink ref="L77" r:id="rId113" xr:uid="{DF218126-DF0D-7C49-BE99-148AE2593E21}"/>
+    <hyperlink ref="L78" r:id="rId114" xr:uid="{C4660B5D-5D54-A94C-BC12-CA44803AD1D0}"/>
+    <hyperlink ref="L79" r:id="rId115" xr:uid="{00DA7061-8850-A540-B1C0-155DC0862069}"/>
+    <hyperlink ref="L80" r:id="rId116" xr:uid="{5FF36B1B-3EE4-5C4E-B470-5AF650167F99}"/>
+    <hyperlink ref="L81" r:id="rId117" xr:uid="{15E045A1-EE4A-5243-8F7E-B196321A6637}"/>
+    <hyperlink ref="L82" r:id="rId118" xr:uid="{91282FEA-5D27-F747-841F-E3D37BC1DEFD}"/>
+    <hyperlink ref="L83" r:id="rId119" xr:uid="{B6F38B3B-D831-3040-A639-60C2DA250F3F}"/>
+    <hyperlink ref="L84" r:id="rId120" xr:uid="{D6633509-2467-2148-AB75-4D5FB98ED8D1}"/>
+    <hyperlink ref="L85" r:id="rId121" xr:uid="{E15B81E3-9CB7-8C43-9E58-CF3468D75D6B}"/>
+    <hyperlink ref="L86" r:id="rId122" xr:uid="{7A6D9B81-492B-BD47-BA1F-F186A7579D53}"/>
+    <hyperlink ref="L87" r:id="rId123" xr:uid="{DC433B43-779A-A041-A481-3BA0B40760B9}"/>
+    <hyperlink ref="L88" r:id="rId124" xr:uid="{1F82062E-4D14-DE46-8164-CE270BE3B4F3}"/>
+    <hyperlink ref="L89" r:id="rId125" xr:uid="{2B496FCC-E732-6340-959E-18651B300F66}"/>
+    <hyperlink ref="L90" r:id="rId126" xr:uid="{54A68FC8-4D50-A04A-8650-A70349978466}"/>
+    <hyperlink ref="L91" r:id="rId127" xr:uid="{D932AD92-BBC9-484A-9CF3-09506A36D679}"/>
+    <hyperlink ref="L92" r:id="rId128" xr:uid="{7585BC08-85C8-4341-9998-3480E0C6256A}"/>
+    <hyperlink ref="L93" r:id="rId129" xr:uid="{75D7675F-8E3C-5844-981A-CA3245190485}"/>
+    <hyperlink ref="L94" r:id="rId130" xr:uid="{DD5FAF39-8B04-984D-9403-84B2AA9B5E13}"/>
+    <hyperlink ref="L95" r:id="rId131" xr:uid="{0039A37E-A98C-D947-A9B8-ED26414F45B2}"/>
+    <hyperlink ref="L96" r:id="rId132" xr:uid="{97F04313-543E-C949-B1E2-B9BFB2F8137A}"/>
+    <hyperlink ref="L97" r:id="rId133" xr:uid="{C643A358-857A-F84A-9E19-7999AC140724}"/>
+    <hyperlink ref="L98" r:id="rId134" xr:uid="{DFDAF174-DA3F-944B-8E3C-7E27FDBD0A8E}"/>
+    <hyperlink ref="L99" r:id="rId135" xr:uid="{1722DBD9-3981-C34C-95FB-29A193329348}"/>
+    <hyperlink ref="L100" r:id="rId136" xr:uid="{48003542-293D-EC4A-8092-2053D089A749}"/>
+    <hyperlink ref="L101" r:id="rId137" xr:uid="{C05EE418-B5E9-B540-A913-AE1E71CBEEA1}"/>
+    <hyperlink ref="L102" r:id="rId138" xr:uid="{6E6E7950-EA9E-4148-A4B1-73942DB1BD42}"/>
+    <hyperlink ref="L62" r:id="rId139" xr:uid="{0A84D223-1D84-214C-AF78-A76B600BBDA1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
